--- a/Sample_run/1/student/duyldhe176352/TC6/GradeDetail.xlsx
+++ b/Sample_run/1/student/duyldhe176352/TC6/GradeDetail.xlsx
@@ -213,6 +213,12 @@
   </x:si>
   <x:si>
     <x:t>{"StudentId":"S111","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -239,7 +245,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -254,6 +260,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFF00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -276,7 +287,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -289,8 +300,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -304,6 +318,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -976,7 +994,7 @@
     <x:col min="8" max="8" width="143.853482" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
@@ -1089,7 +1107,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35952</x:v>
+        <x:v>41698</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1148,7 +1166,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>35952</x:v>
+        <x:v>41698</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1201,7 +1219,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35952</x:v>
+        <x:v>41698</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1257,7 +1275,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35952</x:v>
+        <x:v>41698</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1316,7 +1334,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35952</x:v>
+        <x:v>41698</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>48</x:v>
@@ -1372,7 +1390,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>35952</x:v>
+        <x:v>41698</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>58</x:v>
@@ -1425,7 +1443,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>35952</x:v>
+        <x:v>41698</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1484,7 +1502,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>35952</x:v>
+        <x:v>41698</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1537,7 +1555,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>35952</x:v>
+        <x:v>41698</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1593,7 +1611,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>35952</x:v>
+        <x:v>41698</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1652,7 +1670,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q12" s="0">
-        <x:v>35952</x:v>
+        <x:v>41698</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
         <x:v>58</x:v>
@@ -1705,7 +1723,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>54216</x:v>
+        <x:v>51040</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1764,7 +1782,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>54216</x:v>
+        <x:v>51040</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1817,7 +1835,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>54216</x:v>
+        <x:v>51040</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1873,7 +1891,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>54216</x:v>
+        <x:v>51040</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1932,7 +1950,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>54216</x:v>
+        <x:v>51040</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>48</x:v>
@@ -1988,7 +2006,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q18" s="0">
-        <x:v>54216</x:v>
+        <x:v>51040</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
         <x:v>58</x:v>
@@ -2041,7 +2059,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>54216</x:v>
+        <x:v>51040</x:v>
       </x:c>
       <x:c r="Q19" s="0">
         <x:v>4000</x:v>
@@ -2100,7 +2118,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>54216</x:v>
+        <x:v>51040</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>58</x:v>
@@ -2144,22 +2162,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N21" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
-        <x:v>54216</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q21" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R21" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>51040</x:v>
+      </x:c>
+      <x:c r="R21" s="2" t="s">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:18">
@@ -2209,7 +2227,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>54216</x:v>
+        <x:v>51040</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
@@ -2250,28 +2268,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M23" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N23" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P23" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q23" s="0">
-        <x:v>54216</x:v>
-      </x:c>
-      <x:c r="R23" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q23" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R23" s="4" t="s">
+        <x:v>66</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
